--- a/E/SNK06D.xlsx
+++ b/E/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="516">
   <si>
     <t/>
   </si>
@@ -880,12 +880,6 @@
     <t>TIC TIC STCK BWNG 70</t>
   </si>
   <si>
-    <t>20103371</t>
-  </si>
-  <si>
-    <t>TIC TIC STK BWG+SS65</t>
-  </si>
-  <si>
     <t>20072575</t>
   </si>
   <si>
@@ -1069,6 +1063,15 @@
     <t>M/SK GIM BORI BIG 3G</t>
   </si>
   <si>
+    <t>20143287</t>
+  </si>
+  <si>
+    <t>JYO KOR SWD ORI 4.8</t>
+  </si>
+  <si>
+    <t>,(E-27H)</t>
+  </si>
+  <si>
     <t>20054034</t>
   </si>
   <si>
@@ -1411,19 +1414,13 @@
     <t>IDM KCNG BUMBU 100G</t>
   </si>
   <si>
-    <t>20072316</t>
-  </si>
-  <si>
-    <t>D/K SUKRO KEDELE 95G</t>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
   </si>
   <si>
     <t>36</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
   </si>
   <si>
     <t>20084707</t>
@@ -1954,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4558,10 +4555,10 @@
         <v>286</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4578,10 +4575,10 @@
         <v>286</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,10 +4592,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>42</v>
@@ -4606,19 +4603,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>42</v>
@@ -4635,13 +4632,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,13 +4652,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,10 +4672,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>42</v>
@@ -4695,10 +4692,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>42</v>
@@ -4706,19 +4703,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>42</v>
@@ -4735,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>42</v>
@@ -4755,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>42</v>
@@ -4775,10 +4772,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>42</v>
@@ -4795,10 +4792,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>42</v>
@@ -4806,19 +4803,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>42</v>
@@ -4835,13 +4832,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,10 +4852,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>19</v>
@@ -4875,13 +4872,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,33 +4892,33 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,10 +4932,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>42</v>
@@ -4955,13 +4952,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>89</v>
@@ -4995,13 +4992,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5015,10 +5012,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>42</v>
@@ -5035,30 +5032,30 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>19</v>
@@ -5075,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>19</v>
@@ -5095,13 +5092,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,27 +5112,27 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>42</v>
+        <v>352</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>33</v>
@@ -5146,16 +5143,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>18</v>
@@ -5166,16 +5163,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>4</v>
@@ -5186,16 +5183,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -5206,16 +5203,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>12</v>
@@ -5226,16 +5223,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>15</v>
@@ -5246,16 +5243,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>30</v>
@@ -5266,16 +5263,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>33</v>
@@ -5286,16 +5283,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>4</v>
@@ -5306,16 +5303,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>8</v>
@@ -5326,16 +5323,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>12</v>
@@ -5346,16 +5343,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>15</v>
@@ -5366,16 +5363,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>30</v>
@@ -5386,16 +5383,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>33</v>
@@ -5406,16 +5403,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5426,16 +5423,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>8</v>
@@ -5446,16 +5443,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>12</v>
@@ -5466,16 +5463,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>15</v>
@@ -5486,16 +5483,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>30</v>
@@ -5506,16 +5503,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -5526,16 +5523,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5546,16 +5543,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
@@ -5566,16 +5563,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>15</v>
@@ -5586,16 +5583,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>30</v>
@@ -5606,16 +5603,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>33</v>
@@ -5626,16 +5623,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>18</v>
@@ -5646,16 +5643,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>85</v>
@@ -5666,16 +5663,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>88</v>
@@ -5686,16 +5683,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>4</v>
@@ -5706,16 +5703,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>8</v>
@@ -5726,16 +5723,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
@@ -5746,16 +5743,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>15</v>
@@ -5766,16 +5763,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>30</v>
@@ -5786,16 +5783,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>33</v>
@@ -5806,16 +5803,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>18</v>
@@ -5826,16 +5823,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -5846,16 +5843,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -5866,16 +5863,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>12</v>
@@ -5886,16 +5883,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>15</v>
@@ -5906,16 +5903,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>30</v>
@@ -5926,16 +5923,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>33</v>
@@ -5946,16 +5943,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>4</v>
@@ -5966,16 +5963,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>8</v>
@@ -5986,16 +5983,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>12</v>
@@ -6006,16 +6003,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>15</v>
@@ -6026,16 +6023,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>30</v>
@@ -6046,16 +6043,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>4</v>
@@ -6066,16 +6063,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>8</v>
@@ -6086,16 +6083,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>12</v>
@@ -6106,16 +6103,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>15</v>
@@ -6126,16 +6123,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>30</v>
@@ -6146,16 +6143,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>33</v>
@@ -6166,16 +6163,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>18</v>
@@ -6186,19 +6183,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6206,19 +6203,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6226,19 +6223,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>42</v>
@@ -6246,19 +6243,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>42</v>
@@ -6266,19 +6263,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>42</v>
@@ -6286,19 +6283,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>42</v>
@@ -6306,19 +6303,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>42</v>
@@ -6326,39 +6323,39 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>89</v>
@@ -6366,19 +6363,19 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>89</v>
@@ -6386,19 +6383,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>89</v>
@@ -6406,19 +6403,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>89</v>
@@ -6426,79 +6423,79 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>42</v>
@@ -6506,39 +6503,39 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B229" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>89</v>
@@ -6546,39 +6543,39 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>42</v>
@@ -6586,19 +6583,19 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>42</v>
@@ -6606,19 +6603,19 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>42</v>
@@ -6626,41 +6623,21 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F235" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/E/SNK06D.xlsx
+++ b/E/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
   <si>
     <t/>
   </si>
@@ -124,7 +124,7 @@
     <t>20116686</t>
   </si>
   <si>
-    <t>CHTATO LITE C/ONN 68</t>
+    <t>C/LITE SRCRM ONION65</t>
   </si>
   <si>
     <t>20131037</t>
@@ -163,7 +163,7 @@
     <t>20116684</t>
   </si>
   <si>
-    <t>CHTATO LITE SLMON 68</t>
+    <t>C/LITE SLMON TRYKI65</t>
   </si>
   <si>
     <t>20139713</t>
@@ -1067,9 +1067,6 @@
   </si>
   <si>
     <t>JYO KOR SWD ORI 4.8</t>
-  </si>
-  <si>
-    <t>,(E-27H)</t>
   </si>
   <si>
     <t>20054034</t>
@@ -5118,15 +5115,15 @@
         <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>352</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -5143,10 +5140,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -5163,16 +5160,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>4</v>
@@ -5183,16 +5180,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -5203,16 +5200,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>12</v>
@@ -5223,16 +5220,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>15</v>
@@ -5243,16 +5240,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>30</v>
@@ -5263,16 +5260,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>33</v>
@@ -5283,16 +5280,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>4</v>
@@ -5303,16 +5300,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>8</v>
@@ -5323,16 +5320,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>12</v>
@@ -5343,16 +5340,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>15</v>
@@ -5363,16 +5360,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>30</v>
@@ -5383,16 +5380,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>33</v>
@@ -5403,16 +5400,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5423,16 +5420,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>8</v>
@@ -5443,16 +5440,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>12</v>
@@ -5463,16 +5460,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>15</v>
@@ -5483,16 +5480,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>30</v>
@@ -5503,16 +5500,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -5523,16 +5520,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5543,16 +5540,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
@@ -5563,16 +5560,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>15</v>
@@ -5583,16 +5580,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>30</v>
@@ -5603,16 +5600,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>33</v>
@@ -5623,16 +5620,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>18</v>
@@ -5643,16 +5640,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>85</v>
@@ -5663,16 +5660,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>88</v>
@@ -5683,16 +5680,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>4</v>
@@ -5703,16 +5700,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>8</v>
@@ -5723,16 +5720,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
@@ -5743,16 +5740,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>15</v>
@@ -5763,16 +5760,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>30</v>
@@ -5783,16 +5780,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>33</v>
@@ -5803,16 +5800,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>18</v>
@@ -5823,16 +5820,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -5843,16 +5840,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -5863,16 +5860,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>12</v>
@@ -5883,16 +5880,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>15</v>
@@ -5903,16 +5900,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>30</v>
@@ -5923,16 +5920,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>33</v>
@@ -5943,16 +5940,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>4</v>
@@ -5963,16 +5960,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>8</v>
@@ -5983,16 +5980,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>12</v>
@@ -6003,16 +6000,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>15</v>
@@ -6023,16 +6020,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>30</v>
@@ -6043,16 +6040,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>4</v>
@@ -6063,16 +6060,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>8</v>
@@ -6083,16 +6080,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>12</v>
@@ -6103,16 +6100,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>15</v>
@@ -6123,16 +6120,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>30</v>
@@ -6143,16 +6140,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>33</v>
@@ -6163,16 +6160,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>18</v>
@@ -6183,16 +6180,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>8</v>
@@ -6203,16 +6200,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>12</v>
@@ -6223,16 +6220,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>15</v>
@@ -6243,16 +6240,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>30</v>
@@ -6263,16 +6260,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>33</v>
@@ -6283,16 +6280,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>18</v>
@@ -6303,16 +6300,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>4</v>
@@ -6323,16 +6320,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>8</v>
@@ -6343,16 +6340,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>12</v>
@@ -6363,16 +6360,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>15</v>
@@ -6383,16 +6380,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>30</v>
@@ -6403,16 +6400,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>33</v>
@@ -6423,16 +6420,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
@@ -6443,16 +6440,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>85</v>
@@ -6463,16 +6460,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>88</v>
@@ -6483,16 +6480,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>111</v>
@@ -6503,16 +6500,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>4</v>
@@ -6523,16 +6520,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
@@ -6543,16 +6540,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>12</v>
@@ -6563,16 +6560,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>15</v>
@@ -6583,16 +6580,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>30</v>
@@ -6603,16 +6600,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>33</v>
@@ -6623,16 +6620,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>18</v>

--- a/E/SNK06D.xlsx
+++ b/E/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="522">
   <si>
     <t/>
   </si>
@@ -1159,15 +1159,21 @@
     <t>TARO SNACK BARBQ 32G</t>
   </si>
   <si>
+    <t>20143734</t>
+  </si>
+  <si>
+    <t>CHOCLTS PLW CHCO97.5</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>20097777</t>
   </si>
   <si>
     <t>KRISBEE PLW CHO 100G</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>20081238</t>
   </si>
   <si>
@@ -1294,13 +1300,28 @@
     <t>MI GEMEZ SPICY 3X26G</t>
   </si>
   <si>
+    <t>20143335</t>
+  </si>
+  <si>
+    <t>MI KRMZ SHR AY PGG4S</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>10035883</t>
+  </si>
+  <si>
+    <t>GARUDA PILUS PDS 80G</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
     <t>20092875</t>
   </si>
   <si>
     <t>GRUDA PILUS MI GR 80</t>
-  </si>
-  <si>
-    <t>33</t>
   </si>
   <si>
     <t>20040528</t>
@@ -1948,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F237"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5415,7 +5436,7 @@
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,7 +5456,7 @@
         <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5509,30 +5530,30 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>42</v>
@@ -5549,10 +5570,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>42</v>
@@ -5569,10 +5590,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>42</v>
@@ -5589,10 +5610,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>42</v>
@@ -5609,10 +5630,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>42</v>
@@ -5629,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>42</v>
@@ -5649,10 +5670,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>42</v>
@@ -5669,10 +5690,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>42</v>
@@ -5689,10 +5710,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>42</v>
@@ -5700,19 +5721,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>42</v>
@@ -5729,13 +5750,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5749,13 +5770,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5769,10 +5790,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>9</v>
@@ -5789,13 +5810,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5809,10 +5830,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>42</v>
@@ -5829,10 +5850,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>42</v>
@@ -5840,22 +5861,22 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F195" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5869,10 +5890,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>42</v>
@@ -5880,19 +5901,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>42</v>
@@ -5900,19 +5921,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>42</v>
@@ -5920,19 +5941,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>42</v>
@@ -5940,19 +5961,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>42</v>
@@ -5969,10 +5990,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>42</v>
@@ -5989,10 +6010,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>42</v>
@@ -6009,10 +6030,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>42</v>
@@ -6020,39 +6041,39 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>42</v>
@@ -6069,10 +6090,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>42</v>
@@ -6089,13 +6110,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6109,10 +6130,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>42</v>
@@ -6120,19 +6141,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="E209" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>42</v>
@@ -6140,19 +6161,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>42</v>
@@ -6160,19 +6181,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>42</v>
@@ -6180,19 +6201,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6209,10 +6230,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6229,10 +6250,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>42</v>
@@ -6249,10 +6270,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>42</v>
@@ -6260,19 +6281,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>42</v>
@@ -6280,19 +6301,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>42</v>
@@ -6300,19 +6321,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>42</v>
@@ -6329,13 +6350,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6349,13 +6370,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6369,30 +6390,30 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>89</v>
@@ -6400,19 +6421,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>89</v>
@@ -6420,39 +6441,39 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>89</v>
@@ -6460,59 +6481,59 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>89</v>
@@ -6529,13 +6550,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6549,10 +6570,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>42</v>
@@ -6569,50 +6590,50 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="E232" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>42</v>
@@ -6620,21 +6641,81 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E234" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E237" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F234" s="1" t="s">
+      <c r="F237" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/E/SNK06D.xlsx
+++ b/E/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="521">
   <si>
     <t/>
   </si>
@@ -1177,7 +1177,7 @@
     <t>20081238</t>
   </si>
   <si>
-    <t>TARO NET TRYK BBQ 62</t>
+    <t>TARO NET TRYK BBQ 65</t>
   </si>
   <si>
     <t>20055205</t>
@@ -1306,9 +1306,6 @@
     <t>MI KRMZ SHR AY PGG4S</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>10035883</t>
   </si>
   <si>
@@ -1405,13 +1402,13 @@
     <t>10029724</t>
   </si>
   <si>
-    <t>GARUDA KCNG ATOM 100</t>
+    <t>GARUDA KCNG ATOM 95</t>
   </si>
   <si>
     <t>10003840</t>
   </si>
   <si>
-    <t>GARUDA KCG.TELUR 110</t>
+    <t>GARUDA KCG.TELUR 100</t>
   </si>
   <si>
     <t>20136516</t>
@@ -1456,13 +1453,13 @@
     <t>20120796</t>
   </si>
   <si>
-    <t>GRUDA ROSTA JG.B 95</t>
+    <t>GRUDA ROSTA JG.B 90</t>
   </si>
   <si>
     <t>20089490</t>
   </si>
   <si>
-    <t>GARUDA ROSTA PDS 90G</t>
+    <t>GARUDA ROSTA PDS 85G</t>
   </si>
   <si>
     <t>10005355</t>
@@ -1525,13 +1522,13 @@
     <t>20056977</t>
   </si>
   <si>
-    <t>GARUDA ROSTA BWG 95</t>
+    <t>GARUDA ROSTA BWG 90</t>
   </si>
   <si>
     <t>20095753</t>
   </si>
   <si>
-    <t>GRUDA ROSTA WGYU 95</t>
+    <t>GRUDA ROSTA WGYU 90</t>
   </si>
   <si>
     <t>20112944</t>
@@ -5876,21 +5873,21 @@
         <v>85</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>431</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>4</v>
@@ -5901,16 +5898,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>8</v>
@@ -5921,16 +5918,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>12</v>
@@ -5941,16 +5938,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>15</v>
@@ -5961,16 +5958,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>30</v>
@@ -5981,16 +5978,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>33</v>
@@ -6001,16 +5998,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>18</v>
@@ -6021,16 +6018,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>4</v>
@@ -6041,16 +6038,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>8</v>
@@ -6061,16 +6058,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>12</v>
@@ -6081,16 +6078,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>15</v>
@@ -6101,16 +6098,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>30</v>
@@ -6121,16 +6118,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>4</v>
@@ -6141,16 +6138,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>8</v>
@@ -6161,16 +6158,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>12</v>
@@ -6181,16 +6178,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>15</v>
@@ -6201,16 +6198,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>30</v>
@@ -6221,16 +6218,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>33</v>
@@ -6241,16 +6238,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>18</v>
@@ -6261,16 +6258,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>8</v>
@@ -6281,16 +6278,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>12</v>
@@ -6301,16 +6298,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>15</v>
@@ -6321,16 +6318,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>30</v>
@@ -6341,16 +6338,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>33</v>
@@ -6361,16 +6358,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>18</v>
@@ -6381,16 +6378,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
@@ -6401,16 +6398,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>8</v>
@@ -6421,16 +6418,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>12</v>
@@ -6441,16 +6438,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>15</v>
@@ -6461,16 +6458,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>30</v>
@@ -6481,16 +6478,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>33</v>
@@ -6501,16 +6498,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>18</v>
@@ -6521,16 +6518,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>85</v>
@@ -6541,16 +6538,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>88</v>
@@ -6561,16 +6558,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>111</v>
@@ -6581,16 +6578,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>4</v>
@@ -6601,16 +6598,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>8</v>
@@ -6621,16 +6618,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>12</v>
@@ -6641,16 +6638,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>15</v>
@@ -6661,16 +6658,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>30</v>
@@ -6681,16 +6678,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>33</v>
@@ -6701,16 +6698,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>18</v>
